--- a/output/pdf_financials_xlsx/ISTK.xlsx
+++ b/output/pdf_financials_xlsx/ISTK.xlsx
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.04143</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.92088</v>
       </c>
     </row>
     <row r="93">
@@ -2926,7 +2926,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>3.04143</v>
       </c>

--- a/output/pdf_financials_xlsx/ISTK.xlsx
+++ b/output/pdf_financials_xlsx/ISTK.xlsx
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.020376</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.90693</v>
       </c>
     </row>
     <row r="35">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.020376</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.90693</v>
       </c>
     </row>
     <row r="37">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.078067</v>
+        <v>0.057691</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.996571</v>
+        <v>0.089641</v>
       </c>
     </row>
     <row r="49">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/ISTK.xlsx
+++ b/output/pdf_financials_xlsx/ISTK.xlsx
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.531679</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.581286</v>
       </c>
     </row>
     <row r="68">
